--- a/make-phootos-json.xlsx
+++ b/make-phootos-json.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h_nis\Pictures\photo-map-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9568457-7EEE-46E5-AFC1-BD4E11AF34E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A150940E-D5C0-44E5-951D-234E8520B4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="576" yWindow="168" windowWidth="17088" windowHeight="11640" xr2:uid="{270FD96D-7E2B-40ED-830F-9B2F4900FDBD}"/>
+    <workbookView xWindow="576" yWindow="168" windowWidth="22044" windowHeight="11640" xr2:uid="{270FD96D-7E2B-40ED-830F-9B2F4900FDBD}"/>
   </bookViews>
   <sheets>
     <sheet name="make-phptos-json" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="84">
   <si>
     <t xml:space="preserve">    20260330_01-NW-01.JPG</t>
   </si>
@@ -271,6 +272,12 @@
   </si>
   <si>
     <t>]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;div class='thumb'&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;/div&gt;</t>
   </si>
 </sst>
 </file>
@@ -647,8 +654,8 @@
         <v>0</v>
       </c>
       <c r="D2" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B2)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_01-NW-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B2)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_01-NW-01.JPG",</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
@@ -656,8 +663,8 @@
         <v>1</v>
       </c>
       <c r="D3" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B2)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_01-NW-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B2)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_01-NW-01.JPG",</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
@@ -665,8 +672,8 @@
         <v>2</v>
       </c>
       <c r="D4" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B2)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_01-NW-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B2)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_01-NW-01.JPG"</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
@@ -690,8 +697,8 @@
         <v>5</v>
       </c>
       <c r="D7" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B3)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_02-NW-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B3)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_02-NW-01.JPG",</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
@@ -699,8 +706,8 @@
         <v>6</v>
       </c>
       <c r="D8" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B3)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_02-NW-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B3)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_02-NW-01.JPG",</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
@@ -708,8 +715,8 @@
         <v>7</v>
       </c>
       <c r="D9" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B3)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_02-NW-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B3)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_02-NW-01.JPG"</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.45">
@@ -733,8 +740,8 @@
         <v>10</v>
       </c>
       <c r="D12" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B4)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_03-N.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B4)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_03-N.JPG",</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.45">
@@ -742,8 +749,8 @@
         <v>11</v>
       </c>
       <c r="D13" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B4)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_03-N.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B4)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_03-N.JPG",</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
@@ -751,8 +758,8 @@
         <v>12</v>
       </c>
       <c r="D14" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B4)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_03-N.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B4)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_03-N.JPG"</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
@@ -776,8 +783,8 @@
         <v>15</v>
       </c>
       <c r="D17" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B5)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_03-NE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B5)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_03-NE-01.JPG",</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
@@ -785,8 +792,8 @@
         <v>16</v>
       </c>
       <c r="D18" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B5)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_03-NE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B5)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_03-NE-01.JPG",</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
@@ -794,8 +801,8 @@
         <v>17</v>
       </c>
       <c r="D19" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B5)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_03-NE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B5)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_03-NE-01.JPG"</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
@@ -819,8 +826,8 @@
         <v>20</v>
       </c>
       <c r="D22" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B6)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_03-NW-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B6)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_03-NW-01.JPG",</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
@@ -828,8 +835,8 @@
         <v>21</v>
       </c>
       <c r="D23" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B6)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_03-NW-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B6)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_03-NW-01.JPG",</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
@@ -837,8 +844,8 @@
         <v>22</v>
       </c>
       <c r="D24" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B6)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_03-NW-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B6)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_03-NW-01.JPG"</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
@@ -862,8 +869,8 @@
         <v>25</v>
       </c>
       <c r="D27" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B7)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_03-NW-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B7)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_03-NW-02.JPG",</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.45">
@@ -871,8 +878,8 @@
         <v>26</v>
       </c>
       <c r="D28" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B7)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_03-NW-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B7)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_03-NW-02.JPG",</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.45">
@@ -880,8 +887,8 @@
         <v>27</v>
       </c>
       <c r="D29" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B7)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_03-NW-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B7)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_03-NW-02.JPG"</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.45">
@@ -905,8 +912,8 @@
         <v>30</v>
       </c>
       <c r="D32" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B8)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_03-NW-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B8)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_03-NW-03.JPG",</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.45">
@@ -914,8 +921,8 @@
         <v>31</v>
       </c>
       <c r="D33" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B8)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_03-NW-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B8)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_03-NW-03.JPG",</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
@@ -923,8 +930,8 @@
         <v>32</v>
       </c>
       <c r="D34" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B8)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_03-NW-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B8)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_03-NW-03.JPG"</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
@@ -948,8 +955,8 @@
         <v>35</v>
       </c>
       <c r="D37" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B9)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_03-NW-04.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B9)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_03-NW-04.JPG",</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.45">
@@ -957,8 +964,8 @@
         <v>36</v>
       </c>
       <c r="D38" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B9)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_03-NW-04.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B9)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_03-NW-04.JPG",</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
@@ -966,8 +973,8 @@
         <v>37</v>
       </c>
       <c r="D39" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B9)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_03-NW-04.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B9)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_03-NW-04.JPG"</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.45">
@@ -991,8 +998,8 @@
         <v>40</v>
       </c>
       <c r="D42" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B10)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_04-NE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B10)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_04-NE-01.JPG",</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
@@ -1000,8 +1007,8 @@
         <v>41</v>
       </c>
       <c r="D43" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B10)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_04-NE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B10)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_04-NE-01.JPG",</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.45">
@@ -1009,8 +1016,8 @@
         <v>42</v>
       </c>
       <c r="D44" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B10)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_04-NE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B10)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_04-NE-01.JPG"</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.45">
@@ -1034,8 +1041,8 @@
         <v>45</v>
       </c>
       <c r="D47" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B11)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_04-NE-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B11)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_04-NE-02.JPG",</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.45">
@@ -1043,8 +1050,8 @@
         <v>46</v>
       </c>
       <c r="D48" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B11)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_04-NE-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B11)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_04-NE-02.JPG",</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.45">
@@ -1052,8 +1059,8 @@
         <v>47</v>
       </c>
       <c r="D49" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B11)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_04-NE-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B11)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_04-NE-02.JPG"</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.45">
@@ -1077,8 +1084,8 @@
         <v>50</v>
       </c>
       <c r="D52" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B12)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_04-NE-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B12)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_04-NE-03.JPG",</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.45">
@@ -1086,8 +1093,8 @@
         <v>51</v>
       </c>
       <c r="D53" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B12)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_04-NE-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B12)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_04-NE-03.JPG",</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.45">
@@ -1095,8 +1102,8 @@
         <v>52</v>
       </c>
       <c r="D54" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B12)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_04-NE-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B12)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_04-NE-03.JPG"</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.45">
@@ -1120,8 +1127,8 @@
         <v>55</v>
       </c>
       <c r="D57" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B13)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_04-NE-04.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B13)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_04-NE-04.JPG",</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.45">
@@ -1129,8 +1136,8 @@
         <v>56</v>
       </c>
       <c r="D58" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B13)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_04-NE-04.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B13)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_04-NE-04.JPG",</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.45">
@@ -1138,8 +1145,8 @@
         <v>57</v>
       </c>
       <c r="D59" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B13)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_04-NE-04.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B13)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_04-NE-04.JPG"</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.45">
@@ -1163,8 +1170,8 @@
         <v>60</v>
       </c>
       <c r="D62" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B14)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_04-NE-05.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B14)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_04-NE-05.JPG",</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.45">
@@ -1172,8 +1179,8 @@
         <v>61</v>
       </c>
       <c r="D63" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B14)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_04-NE-05.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B14)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_04-NE-05.JPG",</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.45">
@@ -1181,8 +1188,8 @@
         <v>62</v>
       </c>
       <c r="D64" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B14)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_04-NE-05.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B14)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_04-NE-05.JPG"</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.45">
@@ -1206,8 +1213,8 @@
         <v>65</v>
       </c>
       <c r="D67" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B15)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_05-NE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B15)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_05-NE-01.JPG",</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.45">
@@ -1215,8 +1222,8 @@
         <v>66</v>
       </c>
       <c r="D68" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B15)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_05-NE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B15)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_05-NE-01.JPG",</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.45">
@@ -1224,8 +1231,8 @@
         <v>67</v>
       </c>
       <c r="D69" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B15)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_05-NE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B15)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_05-NE-01.JPG"</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.45">
@@ -1249,8 +1256,8 @@
         <v>70</v>
       </c>
       <c r="D72" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B16)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_05-W-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B16)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_05-W-01.JPG",</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.45">
@@ -1258,8 +1265,8 @@
         <v>71</v>
       </c>
       <c r="D73" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B16)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_05-W-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B16)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_05-W-01.JPG",</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.45">
@@ -1267,8 +1274,8 @@
         <v>72</v>
       </c>
       <c r="D74" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B16)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_05-W-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B16)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_05-W-01.JPG"</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.45">
@@ -1292,8 +1299,8 @@
         <v>75</v>
       </c>
       <c r="D77" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B17)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_11-NW.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B17)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_11-NW.JPG",</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.45">
@@ -1301,8 +1308,8 @@
         <v>76</v>
       </c>
       <c r="D78" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B17)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_11-NW.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B17)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_11-NW.JPG",</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.45">
@@ -1310,8 +1317,8 @@
         <v>77</v>
       </c>
       <c r="D79" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B17)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_11-NW.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B17)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_11-NW.JPG"</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.45">
@@ -1329,20 +1336,20 @@
     </row>
     <row r="82" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D82" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B18)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_11-W-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B18)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_11-W-01.JPG",</v>
       </c>
     </row>
     <row r="83" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D83" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B18)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_11-W-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B18)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_11-W-01.JPG",</v>
       </c>
     </row>
     <row r="84" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D84" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B18)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_11-W-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B18)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_11-W-01.JPG"</v>
       </c>
     </row>
     <row r="85" spans="4:4" x14ac:dyDescent="0.45">
@@ -1357,20 +1364,20 @@
     </row>
     <row r="87" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D87" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B19)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_11-W-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B19)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_11-W-02.JPG",</v>
       </c>
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D88" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B19)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_11-W-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B19)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_11-W-02.JPG",</v>
       </c>
     </row>
     <row r="89" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D89" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B19)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_11-W-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B19)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_11-W-02.JPG"</v>
       </c>
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.45">
@@ -1385,20 +1392,20 @@
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D92" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B20)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_11-W-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B20)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_11-W-03.JPG",</v>
       </c>
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D93" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B20)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_11-W-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B20)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_11-W-03.JPG",</v>
       </c>
     </row>
     <row r="94" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D94" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B20)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_11-W-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B20)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_11-W-03.JPG"</v>
       </c>
     </row>
     <row r="95" spans="4:4" x14ac:dyDescent="0.45">
@@ -1413,20 +1420,20 @@
     </row>
     <row r="97" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D97" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B21)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_12-NW-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B21)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_12-NW-01.JPG",</v>
       </c>
     </row>
     <row r="98" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D98" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B21)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_12-NW-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B21)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_12-NW-01.JPG",</v>
       </c>
     </row>
     <row r="99" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D99" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B21)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_12-NW-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B21)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_12-NW-01.JPG"</v>
       </c>
     </row>
     <row r="100" spans="4:4" x14ac:dyDescent="0.45">
@@ -1441,20 +1448,20 @@
     </row>
     <row r="102" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D102" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B22)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_12-NW-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B22)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_12-NW-02.JPG",</v>
       </c>
     </row>
     <row r="103" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D103" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B22)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_12-NW-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B22)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_12-NW-02.JPG",</v>
       </c>
     </row>
     <row r="104" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D104" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B22)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_12-NW-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B22)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_12-NW-02.JPG"</v>
       </c>
     </row>
     <row r="105" spans="4:4" x14ac:dyDescent="0.45">
@@ -1469,20 +1476,20 @@
     </row>
     <row r="107" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D107" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B23)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_12-W-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B23)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_12-W-01.JPG",</v>
       </c>
     </row>
     <row r="108" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D108" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B23)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_12-W-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B23)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_12-W-01.JPG",</v>
       </c>
     </row>
     <row r="109" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D109" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B23)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_12-W-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B23)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_12-W-01.JPG"</v>
       </c>
     </row>
     <row r="110" spans="4:4" x14ac:dyDescent="0.45">
@@ -1497,20 +1504,20 @@
     </row>
     <row r="112" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D112" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B24)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_12-W-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B24)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_12-W-02.JPG",</v>
       </c>
     </row>
     <row r="113" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D113" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B24)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_12-W-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B24)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_12-W-02.JPG",</v>
       </c>
     </row>
     <row r="114" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D114" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B24)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_12-W-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B24)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_12-W-02.JPG"</v>
       </c>
     </row>
     <row r="115" spans="4:4" x14ac:dyDescent="0.45">
@@ -1525,20 +1532,20 @@
     </row>
     <row r="117" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D117" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B25)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_13-N-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B25)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_13-N-01.JPG",</v>
       </c>
     </row>
     <row r="118" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D118" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B25)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_13-N-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B25)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_13-N-01.JPG",</v>
       </c>
     </row>
     <row r="119" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D119" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B25)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_13-N-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B25)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_13-N-01.JPG"</v>
       </c>
     </row>
     <row r="120" spans="4:4" x14ac:dyDescent="0.45">
@@ -1553,20 +1560,20 @@
     </row>
     <row r="122" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D122" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B26)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_13-N-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B26)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_13-N-02.JPG",</v>
       </c>
     </row>
     <row r="123" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D123" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B26)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_13-N-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B26)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_13-N-02.JPG",</v>
       </c>
     </row>
     <row r="124" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D124" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B26)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_13-N-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B26)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_13-N-02.JPG"</v>
       </c>
     </row>
     <row r="125" spans="4:4" x14ac:dyDescent="0.45">
@@ -1581,20 +1588,20 @@
     </row>
     <row r="127" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D127" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B27)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_13-NE.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B27)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_13-NE.JPG",</v>
       </c>
     </row>
     <row r="128" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D128" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B27)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_13-NE.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B27)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_13-NE.JPG",</v>
       </c>
     </row>
     <row r="129" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D129" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B27)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_13-NE.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B27)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_13-NE.JPG"</v>
       </c>
     </row>
     <row r="130" spans="4:4" x14ac:dyDescent="0.45">
@@ -1609,20 +1616,20 @@
     </row>
     <row r="132" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D132" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B28)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_13-NW.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B28)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_13-NW.JPG",</v>
       </c>
     </row>
     <row r="133" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D133" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B28)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_13-NW.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B28)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_13-NW.JPG",</v>
       </c>
     </row>
     <row r="134" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D134" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B28)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_13-NW.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B28)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_13-NW.JPG"</v>
       </c>
     </row>
     <row r="135" spans="4:4" x14ac:dyDescent="0.45">
@@ -1637,20 +1644,20 @@
     </row>
     <row r="137" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D137" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B29)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-E-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B29)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-E-01.JPG",</v>
       </c>
     </row>
     <row r="138" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D138" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B29)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-E-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B29)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-E-01.JPG",</v>
       </c>
     </row>
     <row r="139" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D139" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B29)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-E-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B29)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-E-01.JPG"</v>
       </c>
     </row>
     <row r="140" spans="4:4" x14ac:dyDescent="0.45">
@@ -1665,20 +1672,20 @@
     </row>
     <row r="142" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D142" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B30)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-E-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B30)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-E-02.JPG",</v>
       </c>
     </row>
     <row r="143" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D143" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B30)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-E-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B30)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-E-02.JPG",</v>
       </c>
     </row>
     <row r="144" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D144" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B30)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-E-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B30)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-E-02.JPG"</v>
       </c>
     </row>
     <row r="145" spans="4:4" x14ac:dyDescent="0.45">
@@ -1693,20 +1700,20 @@
     </row>
     <row r="147" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D147" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B31)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-E-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B31)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-E-03.JPG",</v>
       </c>
     </row>
     <row r="148" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D148" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B31)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-E-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B31)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-E-03.JPG",</v>
       </c>
     </row>
     <row r="149" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D149" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B31)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-E-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B31)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-E-03.JPG"</v>
       </c>
     </row>
     <row r="150" spans="4:4" x14ac:dyDescent="0.45">
@@ -1721,20 +1728,20 @@
     </row>
     <row r="152" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D152" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B32)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-NE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B32)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-NE-01.JPG",</v>
       </c>
     </row>
     <row r="153" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D153" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B32)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-NE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B32)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-NE-01.JPG",</v>
       </c>
     </row>
     <row r="154" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D154" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B32)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-NE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B32)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-NE-01.JPG"</v>
       </c>
     </row>
     <row r="155" spans="4:4" x14ac:dyDescent="0.45">
@@ -1749,20 +1756,20 @@
     </row>
     <row r="157" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D157" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B33)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-NE-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B33)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-NE-02.JPG",</v>
       </c>
     </row>
     <row r="158" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D158" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B33)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-NE-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B33)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-NE-02.JPG",</v>
       </c>
     </row>
     <row r="159" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D159" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B33)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-NE-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B33)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-NE-02.JPG"</v>
       </c>
     </row>
     <row r="160" spans="4:4" x14ac:dyDescent="0.45">
@@ -1777,20 +1784,20 @@
     </row>
     <row r="162" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D162" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B34)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-SE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B34)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-SE-01.JPG",</v>
       </c>
     </row>
     <row r="163" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D163" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B34)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-SE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B34)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-SE-01.JPG",</v>
       </c>
     </row>
     <row r="164" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D164" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B34)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-SE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B34)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-SE-01.JPG"</v>
       </c>
     </row>
     <row r="165" spans="4:4" x14ac:dyDescent="0.45">
@@ -1805,20 +1812,20 @@
     </row>
     <row r="167" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D167" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B35)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-SE-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B35)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-SE-02.JPG",</v>
       </c>
     </row>
     <row r="168" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D168" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B35)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-SE-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B35)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-SE-02.JPG",</v>
       </c>
     </row>
     <row r="169" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D169" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B35)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-SE-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B35)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-SE-02.JPG"</v>
       </c>
     </row>
     <row r="170" spans="4:4" x14ac:dyDescent="0.45">
@@ -1833,20 +1840,20 @@
     </row>
     <row r="172" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D172" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B36)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_14-SE-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B36)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_14-SE-03.JPG",</v>
       </c>
     </row>
     <row r="173" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D173" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B36)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_14-SE-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B36)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_14-SE-03.JPG",</v>
       </c>
     </row>
     <row r="174" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D174" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B36)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_14-SE-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B36)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_14-SE-03.JPG"</v>
       </c>
     </row>
     <row r="175" spans="4:4" x14ac:dyDescent="0.45">
@@ -1861,20 +1868,20 @@
     </row>
     <row r="177" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D177" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B37)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_20-S-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B37)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_20-S-01.JPG",</v>
       </c>
     </row>
     <row r="178" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D178" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B37)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_20-S-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B37)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_20-S-01.JPG",</v>
       </c>
     </row>
     <row r="179" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D179" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B37)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_20-S-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B37)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_20-S-01.JPG"</v>
       </c>
     </row>
     <row r="180" spans="4:4" x14ac:dyDescent="0.45">
@@ -1889,20 +1896,20 @@
     </row>
     <row r="182" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D182" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B38)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_20-S-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B38)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_20-S-02.JPG",</v>
       </c>
     </row>
     <row r="183" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D183" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B38)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_20-S-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B38)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_20-S-02.JPG",</v>
       </c>
     </row>
     <row r="184" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D184" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B38)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_20-S-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B38)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_20-S-02.JPG"</v>
       </c>
     </row>
     <row r="185" spans="4:4" x14ac:dyDescent="0.45">
@@ -1917,20 +1924,20 @@
     </row>
     <row r="187" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D187" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B39)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_20-S-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B39)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_20-S-03.JPG",</v>
       </c>
     </row>
     <row r="188" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D188" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B39)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_20-S-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B39)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_20-S-03.JPG",</v>
       </c>
     </row>
     <row r="189" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D189" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B39)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_20-S-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B39)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_20-S-03.JPG"</v>
       </c>
     </row>
     <row r="190" spans="4:4" x14ac:dyDescent="0.45">
@@ -1945,20 +1952,20 @@
     </row>
     <row r="192" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D192" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B40)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_20-SE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B40)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_20-SE-01.JPG",</v>
       </c>
     </row>
     <row r="193" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D193" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B40)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_20-SE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B40)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_20-SE-01.JPG",</v>
       </c>
     </row>
     <row r="194" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D194" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B40)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_20-SE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B40)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_20-SE-01.JPG"</v>
       </c>
     </row>
     <row r="195" spans="4:4" x14ac:dyDescent="0.45">
@@ -1973,20 +1980,20 @@
     </row>
     <row r="197" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D197" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B41)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_21-E.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B41)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_21-E.JPG",</v>
       </c>
     </row>
     <row r="198" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D198" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B41)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_21-E.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B41)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_21-E.JPG",</v>
       </c>
     </row>
     <row r="199" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D199" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B41)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_21-E.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B41)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_21-E.JPG"</v>
       </c>
     </row>
     <row r="200" spans="4:4" x14ac:dyDescent="0.45">
@@ -2001,20 +2008,20 @@
     </row>
     <row r="202" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D202" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B42)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_21-W.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B42)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_21-W.JPG",</v>
       </c>
     </row>
     <row r="203" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D203" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B42)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_21-W.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B42)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_21-W.JPG",</v>
       </c>
     </row>
     <row r="204" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D204" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B42)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_21-W.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B42)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_21-W.JPG"</v>
       </c>
     </row>
     <row r="205" spans="4:4" x14ac:dyDescent="0.45">
@@ -2029,20 +2036,20 @@
     </row>
     <row r="207" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D207" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B43)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_22-E.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B43)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_22-E.JPG",</v>
       </c>
     </row>
     <row r="208" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D208" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B43)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_22-E.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B43)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_22-E.JPG",</v>
       </c>
     </row>
     <row r="209" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D209" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B43)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_22-E.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B43)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_22-E.JPG"</v>
       </c>
     </row>
     <row r="210" spans="4:4" x14ac:dyDescent="0.45">
@@ -2057,20 +2064,20 @@
     </row>
     <row r="212" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D212" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B44)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_22-W.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B44)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_22-W.JPG",</v>
       </c>
     </row>
     <row r="213" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D213" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B44)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_22-W.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B44)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_22-W.JPG",</v>
       </c>
     </row>
     <row r="214" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D214" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B44)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_22-W.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B44)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_22-W.JPG"</v>
       </c>
     </row>
     <row r="215" spans="4:4" x14ac:dyDescent="0.45">
@@ -2085,20 +2092,20 @@
     </row>
     <row r="217" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D217" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B45)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_23-E-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B45)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_23-E-01.JPG",</v>
       </c>
     </row>
     <row r="218" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D218" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B45)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_23-E-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B45)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_23-E-01.JPG",</v>
       </c>
     </row>
     <row r="219" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D219" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B45)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_23-E-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B45)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_23-E-01.JPG"</v>
       </c>
     </row>
     <row r="220" spans="4:4" x14ac:dyDescent="0.45">
@@ -2113,20 +2120,20 @@
     </row>
     <row r="222" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D222" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B46)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_23-E-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B46)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_23-E-02.JPG",</v>
       </c>
     </row>
     <row r="223" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D223" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B46)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_23-E-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B46)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_23-E-02.JPG",</v>
       </c>
     </row>
     <row r="224" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D224" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B46)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_23-E-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B46)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_23-E-02.JPG"</v>
       </c>
     </row>
     <row r="225" spans="4:4" x14ac:dyDescent="0.45">
@@ -2141,20 +2148,20 @@
     </row>
     <row r="227" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D227" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B47)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_23-E.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B47)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_23-E.JPG",</v>
       </c>
     </row>
     <row r="228" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D228" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B47)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_23-E.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B47)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_23-E.JPG",</v>
       </c>
     </row>
     <row r="229" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D229" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B47)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_23-E.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B47)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_23-E.JPG"</v>
       </c>
     </row>
     <row r="230" spans="4:4" x14ac:dyDescent="0.45">
@@ -2169,20 +2176,20 @@
     </row>
     <row r="232" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D232" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B48)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_23-SE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B48)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_23-SE-01.JPG",</v>
       </c>
     </row>
     <row r="233" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D233" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B48)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_23-SE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B48)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_23-SE-01.JPG",</v>
       </c>
     </row>
     <row r="234" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D234" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B48)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_23-SE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B48)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_23-SE-01.JPG"</v>
       </c>
     </row>
     <row r="235" spans="4:4" x14ac:dyDescent="0.45">
@@ -2197,20 +2204,20 @@
     </row>
     <row r="237" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D237" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B49)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_23-SE-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B49)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_23-SE-02.JPG",</v>
       </c>
     </row>
     <row r="238" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D238" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B49)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_23-SE-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B49)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_23-SE-02.JPG",</v>
       </c>
     </row>
     <row r="239" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D239" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B49)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_23-SE-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B49)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_23-SE-02.JPG"</v>
       </c>
     </row>
     <row r="240" spans="4:4" x14ac:dyDescent="0.45">
@@ -2225,20 +2232,20 @@
     </row>
     <row r="242" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D242" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B50)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_30-E.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B50)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_30-E.JPG",</v>
       </c>
     </row>
     <row r="243" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D243" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B50)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_30-E.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B50)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_30-E.JPG",</v>
       </c>
     </row>
     <row r="244" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D244" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B50)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_30-E.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B50)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_30-E.JPG"</v>
       </c>
     </row>
     <row r="245" spans="4:4" x14ac:dyDescent="0.45">
@@ -2253,20 +2260,20 @@
     </row>
     <row r="247" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D247" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B51)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_30-SW-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B51)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_30-SW-01.JPG",</v>
       </c>
     </row>
     <row r="248" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D248" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B51)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_30-SW-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B51)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_30-SW-01.JPG",</v>
       </c>
     </row>
     <row r="249" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D249" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B51)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_30-SW-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B51)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_30-SW-01.JPG"</v>
       </c>
     </row>
     <row r="250" spans="4:4" x14ac:dyDescent="0.45">
@@ -2281,20 +2288,20 @@
     </row>
     <row r="252" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D252" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B52)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_30-SW-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B52)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_30-SW-02.JPG",</v>
       </c>
     </row>
     <row r="253" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D253" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B52)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_30-SW-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B52)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_30-SW-02.JPG",</v>
       </c>
     </row>
     <row r="254" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D254" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B52)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_30-SW-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B52)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_30-SW-02.JPG"</v>
       </c>
     </row>
     <row r="255" spans="4:4" x14ac:dyDescent="0.45">
@@ -2309,20 +2316,20 @@
     </row>
     <row r="257" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D257" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B53)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_31-E-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B53)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_31-E-01.JPG",</v>
       </c>
     </row>
     <row r="258" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D258" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B53)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_31-E-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B53)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_31-E-01.JPG",</v>
       </c>
     </row>
     <row r="259" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D259" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B53)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_31-E-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B53)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_31-E-01.JPG"</v>
       </c>
     </row>
     <row r="260" spans="4:4" x14ac:dyDescent="0.45">
@@ -2337,20 +2344,20 @@
     </row>
     <row r="262" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D262" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B54)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_31-E-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B54)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_31-E-02.JPG",</v>
       </c>
     </row>
     <row r="263" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D263" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B54)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_31-E-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B54)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_31-E-02.JPG",</v>
       </c>
     </row>
     <row r="264" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D264" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B54)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_31-E-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B54)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_31-E-02.JPG"</v>
       </c>
     </row>
     <row r="265" spans="4:4" x14ac:dyDescent="0.45">
@@ -2365,20 +2372,20 @@
     </row>
     <row r="267" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D267" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B55)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_31-E-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B55)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_31-E-03.JPG",</v>
       </c>
     </row>
     <row r="268" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D268" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B55)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_31-E-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B55)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_31-E-03.JPG",</v>
       </c>
     </row>
     <row r="269" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D269" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B55)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_31-E-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B55)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_31-E-03.JPG"</v>
       </c>
     </row>
     <row r="270" spans="4:4" x14ac:dyDescent="0.45">
@@ -2393,20 +2400,20 @@
     </row>
     <row r="272" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D272" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B56)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_31-SW-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B56)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_31-SW-01.JPG",</v>
       </c>
     </row>
     <row r="273" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D273" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B56)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_31-SW-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B56)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_31-SW-01.JPG",</v>
       </c>
     </row>
     <row r="274" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D274" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B56)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_31-SW-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B56)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_31-SW-01.JPG"</v>
       </c>
     </row>
     <row r="275" spans="4:4" x14ac:dyDescent="0.45">
@@ -2421,20 +2428,20 @@
     </row>
     <row r="277" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D277" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B57)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_31-SW-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B57)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_31-SW-02.JPG",</v>
       </c>
     </row>
     <row r="278" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D278" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B57)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_31-SW-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B57)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_31-SW-02.JPG",</v>
       </c>
     </row>
     <row r="279" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D279" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B57)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_31-SW-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B57)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_31-SW-02.JPG"</v>
       </c>
     </row>
     <row r="280" spans="4:4" x14ac:dyDescent="0.45">
@@ -2449,20 +2456,20 @@
     </row>
     <row r="282" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D282" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B58)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_32-N.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B58)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_32-N.JPG",</v>
       </c>
     </row>
     <row r="283" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D283" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B58)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_32-N.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B58)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_32-N.JPG",</v>
       </c>
     </row>
     <row r="284" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D284" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B58)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_32-N.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B58)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_32-N.JPG"</v>
       </c>
     </row>
     <row r="285" spans="4:4" x14ac:dyDescent="0.45">
@@ -2477,20 +2484,20 @@
     </row>
     <row r="287" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D287" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B59)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_32-NW.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B59)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_32-NW.JPG",</v>
       </c>
     </row>
     <row r="288" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D288" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B59)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_32-NW.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B59)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_32-NW.JPG",</v>
       </c>
     </row>
     <row r="289" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D289" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B59)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_32-NW.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B59)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_32-NW.JPG"</v>
       </c>
     </row>
     <row r="290" spans="4:4" x14ac:dyDescent="0.45">
@@ -2505,20 +2512,20 @@
     </row>
     <row r="292" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D292" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B60)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_32-SE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B60)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_32-SE-01.JPG",</v>
       </c>
     </row>
     <row r="293" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D293" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B60)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_32-SE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B60)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_32-SE-01.JPG",</v>
       </c>
     </row>
     <row r="294" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D294" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B60)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_32-SE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B60)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_32-SE-01.JPG"</v>
       </c>
     </row>
     <row r="295" spans="4:4" x14ac:dyDescent="0.45">
@@ -2533,20 +2540,20 @@
     </row>
     <row r="297" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D297" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B61)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_32-SW.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B61)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_32-SW.JPG",</v>
       </c>
     </row>
     <row r="298" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D298" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B61)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_32-SW.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B61)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_32-SW.JPG",</v>
       </c>
     </row>
     <row r="299" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D299" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B61)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_32-SW.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B61)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_32-SW.JPG"</v>
       </c>
     </row>
     <row r="300" spans="4:4" x14ac:dyDescent="0.45">
@@ -2561,20 +2568,20 @@
     </row>
     <row r="302" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D302" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B62)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-SW-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B62)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-SW-01.JPG",</v>
       </c>
     </row>
     <row r="303" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D303" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B62)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-SW-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B62)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-SW-01.JPG",</v>
       </c>
     </row>
     <row r="304" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D304" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B62)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-SW-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B62)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-SW-01.JPG"</v>
       </c>
     </row>
     <row r="305" spans="4:4" x14ac:dyDescent="0.45">
@@ -2589,20 +2596,20 @@
     </row>
     <row r="307" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D307" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B63)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-SW-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B63)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-SW-02.JPG",</v>
       </c>
     </row>
     <row r="308" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D308" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B63)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-SW-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B63)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-SW-02.JPG",</v>
       </c>
     </row>
     <row r="309" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D309" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B63)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-SW-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B63)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-SW-02.JPG"</v>
       </c>
     </row>
     <row r="310" spans="4:4" x14ac:dyDescent="0.45">
@@ -2617,20 +2624,20 @@
     </row>
     <row r="312" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D312" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B64)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-SW-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B64)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-SW-03.JPG",</v>
       </c>
     </row>
     <row r="313" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D313" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B64)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-SW-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B64)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-SW-03.JPG",</v>
       </c>
     </row>
     <row r="314" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D314" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B64)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-SW-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B64)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-SW-03.JPG"</v>
       </c>
     </row>
     <row r="315" spans="4:4" x14ac:dyDescent="0.45">
@@ -2645,20 +2652,20 @@
     </row>
     <row r="317" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D317" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B65)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-SW-04.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B65)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-SW-04.JPG",</v>
       </c>
     </row>
     <row r="318" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D318" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B65)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-SW-04.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B65)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-SW-04.JPG",</v>
       </c>
     </row>
     <row r="319" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D319" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B65)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-SW-04.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B65)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-SW-04.JPG"</v>
       </c>
     </row>
     <row r="320" spans="4:4" x14ac:dyDescent="0.45">
@@ -2673,20 +2680,20 @@
     </row>
     <row r="322" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D322" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B66)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-W-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B66)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-W-01.JPG",</v>
       </c>
     </row>
     <row r="323" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D323" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B66)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-W-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B66)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-W-01.JPG",</v>
       </c>
     </row>
     <row r="324" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D324" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B66)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-W-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B66)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-W-01.JPG"</v>
       </c>
     </row>
     <row r="325" spans="4:4" x14ac:dyDescent="0.45">
@@ -2701,20 +2708,20 @@
     </row>
     <row r="327" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D327" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B67)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-W-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B67)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-W-02.JPG",</v>
       </c>
     </row>
     <row r="328" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D328" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B67)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-W-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B67)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-W-02.JPG",</v>
       </c>
     </row>
     <row r="329" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D329" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B67)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-W-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B67)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-W-02.JPG"</v>
       </c>
     </row>
     <row r="330" spans="4:4" x14ac:dyDescent="0.45">
@@ -2729,20 +2736,20 @@
     </row>
     <row r="332" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D332" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B68)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-W-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B68)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-W-03.JPG",</v>
       </c>
     </row>
     <row r="333" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D333" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B68)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-W-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B68)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-W-03.JPG",</v>
       </c>
     </row>
     <row r="334" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D334" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B68)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-W-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B68)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-W-03.JPG"</v>
       </c>
     </row>
     <row r="335" spans="4:4" x14ac:dyDescent="0.45">
@@ -2757,20 +2764,20 @@
     </row>
     <row r="337" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D337" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B69)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_33-W-04.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B69)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_33-W-04.JPG",</v>
       </c>
     </row>
     <row r="338" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D338" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B69)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_33-W-04.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B69)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_33-W-04.JPG",</v>
       </c>
     </row>
     <row r="339" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D339" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B69)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_33-W-04.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B69)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_33-W-04.JPG"</v>
       </c>
     </row>
     <row r="340" spans="4:4" x14ac:dyDescent="0.45">
@@ -2785,20 +2792,20 @@
     </row>
     <row r="342" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D342" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B70)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_42-E-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B70)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_42-E-01.JPG",</v>
       </c>
     </row>
     <row r="343" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D343" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B70)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_42-E-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B70)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_42-E-01.JPG",</v>
       </c>
     </row>
     <row r="344" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D344" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B70)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_42-E-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B70)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_42-E-01.JPG"</v>
       </c>
     </row>
     <row r="345" spans="4:4" x14ac:dyDescent="0.45">
@@ -2813,20 +2820,20 @@
     </row>
     <row r="347" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D347" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B71)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_42-E-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B71)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_42-E-02.JPG",</v>
       </c>
     </row>
     <row r="348" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D348" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B71)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_42-E-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B71)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_42-E-02.JPG",</v>
       </c>
     </row>
     <row r="349" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D349" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B71)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_42-E-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B71)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_42-E-02.JPG"</v>
       </c>
     </row>
     <row r="350" spans="4:4" x14ac:dyDescent="0.45">
@@ -2841,20 +2848,20 @@
     </row>
     <row r="352" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D352" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B72)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_42-E-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B72)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_42-E-03.JPG",</v>
       </c>
     </row>
     <row r="353" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D353" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B72)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_42-E-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B72)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_42-E-03.JPG",</v>
       </c>
     </row>
     <row r="354" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D354" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B72)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_42-E-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B72)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_42-E-03.JPG"</v>
       </c>
     </row>
     <row r="355" spans="4:4" x14ac:dyDescent="0.45">
@@ -2869,20 +2876,20 @@
     </row>
     <row r="357" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D357" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B73)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_43-SE.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B73)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_43-SE.JPG",</v>
       </c>
     </row>
     <row r="358" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D358" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B73)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_43-SE.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B73)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_43-SE.JPG",</v>
       </c>
     </row>
     <row r="359" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D359" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B73)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_43-SE.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B73)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_43-SE.JPG"</v>
       </c>
     </row>
     <row r="360" spans="4:4" x14ac:dyDescent="0.45">
@@ -2897,20 +2904,20 @@
     </row>
     <row r="362" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D362" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B74)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_44-E-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B74)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_44-E-01.JPG",</v>
       </c>
     </row>
     <row r="363" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D363" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B74)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_44-E-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B74)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_44-E-01.JPG",</v>
       </c>
     </row>
     <row r="364" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D364" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B74)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_44-E-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B74)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_44-E-01.JPG"</v>
       </c>
     </row>
     <row r="365" spans="4:4" x14ac:dyDescent="0.45">
@@ -2925,20 +2932,20 @@
     </row>
     <row r="367" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D367" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B75)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_44-E-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B75)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_44-E-02.JPG",</v>
       </c>
     </row>
     <row r="368" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D368" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B75)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_44-E-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B75)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_44-E-02.JPG",</v>
       </c>
     </row>
     <row r="369" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D369" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B75)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_44-E-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B75)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_44-E-02.JPG"</v>
       </c>
     </row>
     <row r="370" spans="4:4" x14ac:dyDescent="0.45">
@@ -2953,20 +2960,20 @@
     </row>
     <row r="372" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D372" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B76)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_44-E-03.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B76)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_44-E-03.JPG",</v>
       </c>
     </row>
     <row r="373" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D373" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B76)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_44-E-03.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B76)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_44-E-03.JPG",</v>
       </c>
     </row>
     <row r="374" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D374" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B76)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_44-E-03.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B76)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_44-E-03.JPG"</v>
       </c>
     </row>
     <row r="375" spans="4:4" x14ac:dyDescent="0.45">
@@ -2981,20 +2988,20 @@
     </row>
     <row r="377" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D377" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B77)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_44-E-04.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B77)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_44-E-04.JPG",</v>
       </c>
     </row>
     <row r="378" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D378" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B77)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_44-E-04.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B77)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_44-E-04.JPG",</v>
       </c>
     </row>
     <row r="379" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D379" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B77)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_44-E-04.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B77)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_44-E-04.JPG"</v>
       </c>
     </row>
     <row r="380" spans="4:4" x14ac:dyDescent="0.45">
@@ -3009,20 +3016,20 @@
     </row>
     <row r="382" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D382" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B78)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_44-NE-01.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B78)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_44-NE-01.JPG",</v>
       </c>
     </row>
     <row r="383" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D383" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B78)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_44-NE-01.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B78)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_44-NE-01.JPG",</v>
       </c>
     </row>
     <row r="384" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D384" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B78)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_44-NE-01.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B78)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_44-NE-01.JPG"</v>
       </c>
     </row>
     <row r="385" spans="4:4" x14ac:dyDescent="0.45">
@@ -3037,20 +3044,20 @@
     </row>
     <row r="387" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D387" t="str">
-        <f>" "&amp;"""file"" ; """&amp;TRIM($B79)&amp;""","</f>
-        <v xml:space="preserve"> "file" ; "20260330_44-NE-02.JPG",</v>
+        <f>" "&amp;"""file"": """&amp;TRIM($B79)&amp;""","</f>
+        <v xml:space="preserve"> "file": "20260330_44-NE-02.JPG",</v>
       </c>
     </row>
     <row r="388" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D388" t="str">
-        <f>" "&amp;"""thumbs"" ; """&amp;"thumbs/"&amp;TRIM($B79)&amp;""","</f>
-        <v xml:space="preserve"> "thumbs" ; "thumbs/20260330_44-NE-02.JPG",</v>
+        <f>" "&amp;"""thumbs"": """&amp;"thumbs/"&amp;TRIM($B79)&amp;""","</f>
+        <v xml:space="preserve"> "thumbs": "thumbs/20260330_44-NE-02.JPG",</v>
       </c>
     </row>
     <row r="389" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D389" t="str">
-        <f>" "&amp;"""full"" ; """&amp;"photos/"&amp;TRIM($B79)&amp;""","</f>
-        <v xml:space="preserve"> "full" ; "photos/20260330_44-NE-02.JPG",</v>
+        <f>" "&amp;"""full"": """&amp;"photos/"&amp;TRIM($B79)&amp;""""</f>
+        <v xml:space="preserve"> "full": "photos/20260330_44-NE-02.JPG"</v>
       </c>
     </row>
     <row r="390" spans="4:4" x14ac:dyDescent="0.45">
@@ -3068,4 +3075,1508 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A7BCF8E-C55C-4878-BBC0-9C11E8FBC20F}">
+  <dimension ref="B2:G80"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="25.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.09765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="str">
+        <f>"      &lt;img src='../thumbs/"&amp;TRIM($B2)&amp;"' alt="&amp;"'"&amp;"'&gt; "</f>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_01-NW-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F2" t="str">
+        <f>"     &lt;span&gt; "&amp;TRIM(B2)&amp;"&lt;/span&gt;"</f>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_01-NW-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E66" si="0">"      &lt;img src='../thumbs/"&amp;TRIM($B3)&amp;"' alt="&amp;"'"&amp;"'&gt; "</f>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_02-NW-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F66" si="1">"     &lt;span&gt; "&amp;TRIM(B3)&amp;"&lt;/span&gt;"</f>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_02-NW-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_03-N.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_03-N.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_03-NE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_03-NE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_03-NW-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_03-NW-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_03-NW-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_03-NW-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_03-NW-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_03-NW-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_03-NW-04.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_03-NW-04.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_04-NE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_04-NE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_04-NE-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_04-NE-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_04-NE-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_04-NE-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_04-NE-04.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_04-NE-04.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_04-NE-05.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_04-NE-05.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_05-NE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_05-NE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_05-W-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_05-W-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_11-NW.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_11-NW.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_11-W-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_11-W-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_11-W-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_11-W-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_11-W-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_11-W-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_12-NW-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_12-NW-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_12-NW-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_12-NW-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_12-W-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_12-W-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_12-W-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_12-W-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_13-N-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_13-N-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_13-N-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_13-N-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_13-NE.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_13-NE.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_13-NW.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_13-NW.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-E-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-E-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-E-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-E-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-E-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-E-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-NE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-NE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-NE-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-NE-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-SE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-SE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-SE-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-SE-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_14-SE-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_14-SE-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_20-S-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_20-S-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G37" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_20-S-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_20-S-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_20-S-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_20-S-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G39" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_20-SE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_20-SE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_21-E.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_21-E.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_21-W.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_21-W.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_22-E.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_22-E.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_22-W.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_22-W.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_23-E-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_23-E-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_23-E-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_23-E-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_23-E.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_23-E.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G47" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_23-SE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_23-SE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_23-SE-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_23-SE-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G49" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_30-E.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_30-E.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_30-SW-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_30-SW-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_30-SW-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_30-SW-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_31-E-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_31-E-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_31-E-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_31-E-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_31-E-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_31-E-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G55" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_31-SW-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_31-SW-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_31-SW-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_31-SW-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_32-N.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_32-N.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_32-NW.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_32-NW.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G59" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>58</v>
+      </c>
+      <c r="D60" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_32-SE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_32-SE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_32-SW.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_32-SW.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-SW-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-SW-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-SW-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-SW-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G63" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>62</v>
+      </c>
+      <c r="D64" t="s">
+        <v>82</v>
+      </c>
+      <c r="E64" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-SW-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-SW-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G64" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-SW-04.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-SW-04.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" t="s">
+        <v>82</v>
+      </c>
+      <c r="E66" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-W-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-W-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G66" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" t="s">
+        <v>82</v>
+      </c>
+      <c r="E67" t="str">
+        <f t="shared" ref="E67:E107" si="2">"      &lt;img src='../thumbs/"&amp;TRIM($B67)&amp;"' alt="&amp;"'"&amp;"'&gt; "</f>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-W-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" ref="F67:F107" si="3">"     &lt;span&gt; "&amp;TRIM(B67)&amp;"&lt;/span&gt;"</f>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-W-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G67" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-W-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F68" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-W-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G68" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+      <c r="D69" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_33-W-04.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F69" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_33-W-04.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_42-E-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F70" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_42-E-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B71" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" t="s">
+        <v>82</v>
+      </c>
+      <c r="E71" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_42-E-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F71" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_42-E-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_42-E-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F72" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_42-E-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>71</v>
+      </c>
+      <c r="D73" t="s">
+        <v>82</v>
+      </c>
+      <c r="E73" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_43-SE.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F73" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_43-SE.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>72</v>
+      </c>
+      <c r="D74" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_44-E-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F74" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_44-E-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G74" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_44-E-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F75" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_44-E-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B76" t="s">
+        <v>74</v>
+      </c>
+      <c r="D76" t="s">
+        <v>82</v>
+      </c>
+      <c r="E76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_44-E-03.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F76" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_44-E-03.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G76" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D77" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_44-E-04.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F77" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_44-E-04.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D78" t="s">
+        <v>82</v>
+      </c>
+      <c r="E78" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_44-NE-01.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F78" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_44-NE-01.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G78" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D79" t="s">
+        <v>82</v>
+      </c>
+      <c r="E79" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">      &lt;img src='../thumbs/20260330_44-NE-02.JPG' alt=''&gt; </v>
+      </c>
+      <c r="F79" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">     &lt;span&gt; 20260330_44-NE-02.JPG&lt;/span&gt;</v>
+      </c>
+      <c r="G79" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>